--- a/pre-week-2/Homework1.xlsx
+++ b/pre-week-2/Homework1.xlsx
@@ -1,26 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Desktop\DataAnalytics\pre-week-2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739A3F57-F224-4AFF-8EF7-0320C27BE8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="11956" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Summary" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Monthly Sales</t>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tore</t>
+    </r>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>The overall average monthly sales performance across the 12 stores is approximately $49.42. The median is $47.50 and the mode is $46, showing that most stores are performing in the mid-40s to low-50s range. Store performance is moderately spread out, with a sample standard deviation of about 7.63 when all stores are included. However, when Store H (72) is temporarily removed, the standard deviation drops dramatically to about 2.91, indicating that performance is actually very tightly grouped among the other 11 stores. Store H is a clear outlier that significantly influences both the mean and the variability of the entire dataset. Additional information I would want includes sales targets or goals for each store, operating costs/profit margins, the time period these numbers represent (seasonality?), and any external factors such as location traffic or promotions.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +89,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,17 +141,225 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +370,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E163EB2A-C46F-4D47-ADB9-970338078EE2}" name="Table1" displayName="Table1" ref="A1:B13" totalsRowShown="0" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
+  <autoFilter ref="A1:B13" xr:uid="{E163EB2A-C46F-4D47-ADB9-970338078EE2}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8028763A-D031-4987-AE95-3AA746B800CB}" name="Store" dataDxfId="0">
+      <calculatedColumnFormula>"Store " &amp; CHAR(64 +ROW(A2) -1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{94A48E42-C82B-4FDE-BD7E-1BB7493A941E}" name="Monthly Sales" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +647,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="str">
+        <f>"Store " &amp; CHAR(64 +ROW(A2) -1)</f>
+        <v>Store A</v>
+      </c>
+      <c r="B2" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="str">
+        <f t="shared" ref="A3:A13" si="0">"Store " &amp; CHAR(64 +ROW(A3) -1)</f>
+        <v>Store B</v>
+      </c>
+      <c r="B3" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store C</v>
+      </c>
+      <c r="B4" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store D</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store E</v>
+      </c>
+      <c r="B6" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store F</v>
+      </c>
+      <c r="B7" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store G</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store H</v>
+      </c>
+      <c r="B9" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store I</v>
+      </c>
+      <c r="B10" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store J</v>
+      </c>
+      <c r="B11" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Store K</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Store L</v>
+      </c>
+      <c r="B13" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2">
+        <f>AVERAGE(B2:B13)</f>
+        <v>49.416666666666664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2">
+        <f>MEDIAN(B2:B13)</f>
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2">
+        <f>_xlfn.MODE.SNGL(B2:B13)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <f>MAX(B2:B13) - MIN(B2:B13)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1">
+        <f>_xlfn.STDEV.S(B2:B13)</f>
+        <v>7.6331613054586773</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B21" s="1">
+        <f>_xlfn.STDEV.S(B2:B8,B10:B13)</f>
+        <v>2.9076701075853588</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687E459F-9E17-46D2-B3FA-342D03A74362}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="59.265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="185.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>